--- a/apps/oracle-fusion/testdata/payables/payment_terms.xlsx
+++ b/apps/oracle-fusion/testdata/payables/payment_terms.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriya\axiom\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriya\axiom\apps\oracle-fusion\testdata\payables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15C1E917-AC33-46D7-B8C4-741230C9CA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDB8125-4231-4C43-BF3D-7D7533748BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CEA518-74DE-486F-B3BF-39C5E59AD1FA}"/>
   </bookViews>
   <sheets>
-    <sheet name="PaymentTerms" sheetId="1" r:id="rId1"/>
+    <sheet name="PaymentTerms" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,24 +34,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t>Action</t>
   </si>
   <si>
-    <t>TermName</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>DueDays</t>
-  </si>
-  <si>
     <t>CREATE</t>
   </si>
   <si>
     <t>Net 30 Demo</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Cutoff Day</t>
+  </si>
+  <si>
+    <t>From Date</t>
+  </si>
+  <si>
+    <t>To Date</t>
+  </si>
+  <si>
+    <t>Due</t>
+  </si>
+  <si>
+    <t>Amount Due</t>
+  </si>
+  <si>
+    <t>Calendar</t>
+  </si>
+  <si>
+    <t>Fixed Date</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Day of Month</t>
+  </si>
+  <si>
+    <t>First Discount Percentage</t>
+  </si>
+  <si>
+    <t>First Discount Days</t>
+  </si>
+  <si>
+    <t>First Discount Day of Month</t>
+  </si>
+  <si>
+    <t>Second Discount Percentage</t>
+  </si>
+  <si>
+    <t>Second Discount Days</t>
+  </si>
+  <si>
+    <t>Second Discount Day of Month</t>
+  </si>
+  <si>
+    <t>Third Discount Percentage</t>
+  </si>
+  <si>
+    <t>Third Discount Days</t>
+  </si>
+  <si>
+    <t>Third Discount Day of Month</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Set Name</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>Net 15 Demo</t>
+  </si>
+  <si>
+    <t>Term Name</t>
+  </si>
+  <si>
+    <t>Line #</t>
+  </si>
+  <si>
+    <t>Discount Line #</t>
+  </si>
+  <si>
+    <t>Object Type</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Term Line</t>
+  </si>
+  <si>
+    <t>COMMON</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>Net 30 Demo1234</t>
+  </si>
+  <si>
+    <t>Net 15 Demo1234</t>
   </si>
 </sst>
 </file>
@@ -67,15 +160,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,18 +182,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,41 +525,309 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65BDCE08-350C-478D-B7CE-007DC84DAF92}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74076634-9EA9-4E53-A365-A9D5B792D07A}">
+  <dimension ref="B6:O21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="6" spans="2:15" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="F8" s="4"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3">
+        <v>30</v>
+      </c>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>100</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3">
+        <v>30</v>
+      </c>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
+        <v>15</v>
+      </c>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>70</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
